--- a/data/valuations/NTSK/NTSK_modelo_valoracion.xlsx
+++ b/data/valuations/NTSK/NTSK_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.4186</v>
+        <v>0.3703</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.37674</v>
+        <v>0.33327</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.3348800000000001</v>
+        <v>0.29624</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.29302</v>
+        <v>0.25921</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.25116</v>
+        <v>0.22218</v>
       </c>
     </row>
     <row r="10">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0.2254</v>
+        <v>0.2737</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.20286</v>
+        <v>0.24633</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.18032</v>
+        <v>0.21896</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.15778</v>
+        <v>0.19159</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.13524</v>
+        <v>0.16422</v>
       </c>
     </row>
     <row r="11">
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0.6420840800670192</v>
+        <v>0.6320840800670192</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.6420840800670192</v>
+        <v>0.6320840800670192</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.6420840800670192</v>
+        <v>0.6320840800670192</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.6420840800670192</v>
+        <v>0.6320840800670192</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.6420840800670192</v>
+        <v>0.6320840800670192</v>
       </c>
     </row>
     <row r="17">
@@ -795,19 +795,19 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.6020840800670192</v>
+        <v>0.6120840800670192</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.6020840800670192</v>
+        <v>0.6120840800670192</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.6020840800670192</v>
+        <v>0.6120840800670192</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6020840800670192</v>
+        <v>0.6120840800670192</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.6020840800670192</v>
+        <v>0.6120840800670192</v>
       </c>
     </row>
     <row r="18">
@@ -844,19 +844,19 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.7320360499586136</v>
+        <v>0.4894530056362105</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.7320360499586136</v>
+        <v>0.4894530056362105</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.7320360499586136</v>
+        <v>0.4894530056362105</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.7320360499586136</v>
+        <v>0.4894530056362105</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.7320360499586136</v>
+        <v>0.4894530056362105</v>
       </c>
     </row>
     <row r="21">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.7220360499586136</v>
+        <v>0.4844530056362105</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.7220360499586136</v>
+        <v>0.4844530056362105</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.7220360499586136</v>
+        <v>0.4844530056362105</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.7220360499586136</v>
+        <v>0.4844530056362105</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.7220360499586136</v>
+        <v>0.4844530056362105</v>
       </c>
     </row>
     <row r="22">
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.7420360499586136</v>
+        <v>0.4944530056362105</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.7420360499586136</v>
+        <v>0.4944530056362105</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.7420360499586136</v>
+        <v>0.4944530056362105</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.7420360499586136</v>
+        <v>0.4944530056362105</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.7420360499586136</v>
+        <v>0.4944530056362105</v>
       </c>
     </row>
     <row r="23">
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.5169904270209683</v>
+        <v>0.5119904270209683</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.5169904270209683</v>
+        <v>0.5119904270209683</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.5169904270209683</v>
+        <v>0.5119904270209683</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.5169904270209683</v>
+        <v>0.5119904270209683</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.5169904270209683</v>
+        <v>0.5119904270209683</v>
       </c>
     </row>
     <row r="28">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.0901</v>
+        <v>0.0905</v>
       </c>
     </row>
     <row r="36">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0801</v>
+        <v>0.0805</v>
       </c>
     </row>
     <row r="37">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1101</v>
+        <v>0.1005</v>
       </c>
     </row>
     <row r="38">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>9.66</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="4">
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="I21" s="8">
-        <f>I12*$C$16</f>
+        <f>I8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/9.66-1</f>
+        <f>C33/7.73-1</f>
         <v/>
       </c>
     </row>
@@ -3275,202 +3275,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>17x</t>
+          <t>21x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>19x</t>
+          <t>23x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>21x</t>
+          <t>25x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>23x</t>
+          <t>27x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>29x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0601</v>
+        <v>0.0605</v>
       </c>
       <c r="C39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$12*17/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*21/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$12*19/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*23/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$12*21/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*25/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$12*23/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*27/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$12*25/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*29/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.0701</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="C40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$12*17/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*21/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$12*19/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*23/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$12*21/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*25/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$12*23/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*27/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$12*25/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*29/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0801</v>
+        <v>0.0805</v>
       </c>
       <c r="C41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$12*17/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*21/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$12*19/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*23/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$12*21/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*25/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$12*23/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*27/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$12*25/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*29/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.0901</v>
+        <v>0.0905</v>
       </c>
       <c r="C42" s="22">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$12*17/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*21/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$12*19/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*23/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$12*21/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*25/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$12*23/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*27/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$12*25/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*29/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.1001</v>
+        <v>0.1005</v>
       </c>
       <c r="C43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$12*17/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*21/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$12*19/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*23/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$12*21/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*25/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$12*23/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*27/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$12*25/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*29/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1101</v>
+        <v>0.1105</v>
       </c>
       <c r="C44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$12*17/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*21/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$12*19/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*23/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$12*21/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*25/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$12*23/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*27/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$12*25/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*29/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1201</v>
+        <v>0.1205</v>
       </c>
       <c r="C45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$12*17/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*21/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$12*19/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*23/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$12*21/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*25/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$12*23/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*27/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$12*25/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*29/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/NTSK/NTSK_modelo_valoracion.xlsx
+++ b/data/valuations/NTSK/NTSK_modelo_valoracion.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -528,6 +529,7 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -578,6 +580,11 @@
       <c r="I4" s="1" t="inlineStr">
         <is>
           <t>FY2030</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>FY2031</t>
         </is>
       </c>
     </row>
@@ -595,6 +602,7 @@
       <c r="G6" s="1" t="n"/>
       <c r="H6" s="1" t="n"/>
       <c r="I6" s="1" t="n"/>
+      <c r="J6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -608,6 +616,9 @@
       <c r="D7" s="5" t="n">
         <v>538.268</v>
       </c>
+      <c r="E7" s="5" t="n">
+        <v>708.997</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -615,20 +626,20 @@
           <t xml:space="preserve">  Revenue Growth - Base</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>0.322</v>
-      </c>
       <c r="F8" s="6" t="n">
-        <v>0.2898</v>
+        <v>0.23</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.2576</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.2254</v>
+        <v>0.17</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.1932</v>
+        <v>0.14</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="9">
@@ -637,20 +648,20 @@
           <t xml:space="preserve">  Revenue Growth - Bull</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>0.3703</v>
-      </c>
       <c r="F9" s="6" t="n">
-        <v>0.33327</v>
+        <v>0.28</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.29624</v>
+        <v>0.25</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.25921</v>
+        <v>0.22</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.22218</v>
+        <v>0.18</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="10">
@@ -659,20 +670,20 @@
           <t xml:space="preserve">  Revenue Growth - Bear</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>0.2737</v>
-      </c>
       <c r="F10" s="6" t="n">
-        <v>0.24633</v>
+        <v>0.2</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.21896</v>
+        <v>0.16</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.19159</v>
+        <v>0.12</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.16422</v>
+        <v>0.1</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="11">
@@ -681,10 +692,6 @@
           <t xml:space="preserve">  Revenue Growth (Selected)</t>
         </is>
       </c>
-      <c r="E11" s="7">
-        <f>OFFSET(E8,$G$2-1,0)</f>
-        <v/>
-      </c>
       <c r="F11" s="7">
         <f>OFFSET(F8,$G$2-1,0)</f>
         <v/>
@@ -701,6 +708,10 @@
         <f>OFFSET(I8,$G$2-1,0)</f>
         <v/>
       </c>
+      <c r="J11" s="7">
+        <f>OFFSET(J8,$G$2-1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -708,12 +719,8 @@
           <t xml:space="preserve">  Revenue Projected ($M)</t>
         </is>
       </c>
-      <c r="E12" s="8">
-        <f>D7*(1+E11)</f>
-        <v/>
-      </c>
       <c r="F12" s="8">
-        <f>E12*(1+F11)</f>
+        <f>E7*(1+F11)</f>
         <v/>
       </c>
       <c r="G12" s="8">
@@ -726,6 +733,10 @@
       </c>
       <c r="I12" s="8">
         <f>H12*(1+I11)</f>
+        <v/>
+      </c>
+      <c r="J12" s="8">
+        <f>I12*(1+J11)</f>
         <v/>
       </c>
     </row>
@@ -743,6 +754,7 @@
       <c r="G14" s="1" t="n"/>
       <c r="H14" s="1" t="n"/>
       <c r="I14" s="1" t="n"/>
+      <c r="J14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -750,20 +762,20 @@
           <t>Gross Margin - Base</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>0.6220840800670192</v>
-      </c>
       <c r="F15" s="6" t="n">
-        <v>0.6220840800670192</v>
+        <v>0.7</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.6220840800670192</v>
+        <v>0.7</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.6220840800670192</v>
+        <v>0.7</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.6220840800670192</v>
+        <v>0.7</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="16">
@@ -772,20 +784,20 @@
           <t>Gross Margin - Bull</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>0.6320840800670192</v>
-      </c>
       <c r="F16" s="6" t="n">
-        <v>0.6320840800670192</v>
+        <v>0.72</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.6320840800670192</v>
+        <v>0.72</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.6320840800670192</v>
+        <v>0.72</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.6320840800670192</v>
+        <v>0.72</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="17">
@@ -794,20 +806,20 @@
           <t>Gross Margin - Bear</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n">
-        <v>0.6120840800670192</v>
-      </c>
       <c r="F17" s="6" t="n">
-        <v>0.6120840800670192</v>
+        <v>0.68</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.6120840800670192</v>
+        <v>0.68</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6120840800670192</v>
+        <v>0.68</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.6120840800670192</v>
+        <v>0.68</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="18">
@@ -816,10 +828,6 @@
           <t>Gross Margin (Selected)</t>
         </is>
       </c>
-      <c r="E18" s="7">
-        <f>OFFSET(E15,$G$2-1,0)</f>
-        <v/>
-      </c>
       <c r="F18" s="7">
         <f>OFFSET(F15,$G$2-1,0)</f>
         <v/>
@@ -836,6 +844,10 @@
         <f>OFFSET(I15,$G$2-1,0)</f>
         <v/>
       </c>
+      <c r="J18" s="7">
+        <f>OFFSET(J15,$G$2-1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -843,20 +855,20 @@
           <t>SG&amp;A % Revenue - Base</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
-        <v>0.4894530056362105</v>
-      </c>
       <c r="F20" s="6" t="n">
-        <v>0.4894530056362105</v>
+        <v>0.4</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.4894530056362105</v>
+        <v>0.4</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.4894530056362105</v>
+        <v>0.4</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.4894530056362105</v>
+        <v>0.4</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="21">
@@ -865,20 +877,20 @@
           <t>SG&amp;A % Revenue - Bull</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
-        <v>0.4844530056362105</v>
-      </c>
       <c r="F21" s="6" t="n">
-        <v>0.4844530056362105</v>
+        <v>0.35</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.4844530056362105</v>
+        <v>0.35</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.4844530056362105</v>
+        <v>0.35</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.4844530056362105</v>
+        <v>0.35</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="22">
@@ -887,20 +899,20 @@
           <t>SG&amp;A % Revenue - Bear</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
-        <v>0.4944530056362105</v>
-      </c>
       <c r="F22" s="6" t="n">
-        <v>0.4944530056362105</v>
+        <v>0.45</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.4944530056362105</v>
+        <v>0.45</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.4944530056362105</v>
+        <v>0.45</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4944530056362105</v>
+        <v>0.45</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="23">
@@ -909,10 +921,6 @@
           <t>SG&amp;A % Revenue (Selected)</t>
         </is>
       </c>
-      <c r="E23" s="7">
-        <f>OFFSET(E20,$G$2-1,0)</f>
-        <v/>
-      </c>
       <c r="F23" s="7">
         <f>OFFSET(F20,$G$2-1,0)</f>
         <v/>
@@ -929,6 +937,10 @@
         <f>OFFSET(I20,$G$2-1,0)</f>
         <v/>
       </c>
+      <c r="J23" s="7">
+        <f>OFFSET(J20,$G$2-1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -936,20 +948,20 @@
           <t>R&amp;D % Revenue - Base</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n">
-        <v>0.5119904270209683</v>
-      </c>
       <c r="F25" s="6" t="n">
-        <v>0.5119904270209683</v>
+        <v>0.18</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.5119904270209683</v>
+        <v>0.18</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.5119904270209683</v>
+        <v>0.18</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.5119904270209683</v>
+        <v>0.18</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="26">
@@ -958,20 +970,20 @@
           <t>R&amp;D % Revenue - Bull</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n">
-        <v>0.5119904270209683</v>
-      </c>
       <c r="F26" s="6" t="n">
-        <v>0.5119904270209683</v>
+        <v>0.17</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.5119904270209683</v>
+        <v>0.17</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.5119904270209683</v>
+        <v>0.17</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.5119904270209683</v>
+        <v>0.17</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="27">
@@ -980,20 +992,20 @@
           <t>R&amp;D % Revenue - Bear</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n">
-        <v>0.5119904270209683</v>
-      </c>
       <c r="F27" s="6" t="n">
-        <v>0.5119904270209683</v>
+        <v>0.2</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.5119904270209683</v>
+        <v>0.2</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.5119904270209683</v>
+        <v>0.2</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.5119904270209683</v>
+        <v>0.2</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="28">
@@ -1002,10 +1014,6 @@
           <t>R&amp;D % Revenue (Selected)</t>
         </is>
       </c>
-      <c r="E28" s="7">
-        <f>OFFSET(E25,$G$2-1,0)</f>
-        <v/>
-      </c>
       <c r="F28" s="7">
         <f>OFFSET(F25,$G$2-1,0)</f>
         <v/>
@@ -1022,6 +1030,10 @@
         <f>OFFSET(I25,$G$2-1,0)</f>
         <v/>
       </c>
+      <c r="J28" s="7">
+        <f>OFFSET(J25,$G$2-1,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1029,20 +1041,20 @@
           <t>D&amp;A % Revenue</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n">
-        <v>0.1087667770661427</v>
-      </c>
       <c r="F30" s="6" t="n">
-        <v>0.1087667770661427</v>
+        <v>0.05</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.1087667770661427</v>
+        <v>0.05</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.1087667770661427</v>
+        <v>0.05</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.1087667770661427</v>
+        <v>0.05</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="31">
@@ -1051,20 +1063,20 @@
           <t>CapEx % Revenue</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
-        <v>0.08811803001061608</v>
-      </c>
       <c r="F31" s="6" t="n">
-        <v>0.08811803001061608</v>
+        <v>0.05</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.08811803001061608</v>
+        <v>0.05</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.08811803001061608</v>
+        <v>0.05</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.08811803001061608</v>
+        <v>0.05</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="32">
@@ -1073,9 +1085,6 @@
           <t>Tax Rate</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n">
-        <v>0.21</v>
-      </c>
       <c r="F32" s="6" t="n">
         <v>0.21</v>
       </c>
@@ -1086,6 +1095,9 @@
         <v>0.21</v>
       </c>
       <c r="I32" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J32" s="6" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -1103,6 +1115,7 @@
       <c r="G34" s="1" t="n"/>
       <c r="H34" s="1" t="n"/>
       <c r="I34" s="1" t="n"/>
+      <c r="J34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1111,7 +1124,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.0905</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="36">
@@ -1121,7 +1134,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0805</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="37">
@@ -1131,7 +1144,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1005</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="38">
@@ -1152,7 +1165,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
@@ -1162,7 +1175,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -1172,7 +1185,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -1198,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1210,6 +1223,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1221,6 +1235,7 @@
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1236,6 +1251,11 @@
       <c r="D3" s="1" t="inlineStr">
         <is>
           <t>FY2025</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>FY2026</t>
         </is>
       </c>
     </row>
@@ -1248,6 +1268,7 @@
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="1" t="n"/>
       <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1261,6 +1282,9 @@
       <c r="D6" s="5" t="n">
         <v>538.268</v>
       </c>
+      <c r="E6" s="5" t="n">
+        <v>708.997</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1274,6 +1298,9 @@
       <c r="D7" s="5" t="n">
         <v>190.369</v>
       </c>
+      <c r="E7" s="5" t="n">
+        <v>226.328</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1287,6 +1314,9 @@
       <c r="D8" s="5" t="n">
         <v>347.899</v>
       </c>
+      <c r="E8" s="5" t="n">
+        <v>482.669</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1300,6 +1330,9 @@
       <c r="D9" s="11" t="n">
         <v>0.6463304524883515</v>
       </c>
+      <c r="E9" s="11" t="n">
+        <v>0.680777210622894</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1313,6 +1346,9 @@
       <c r="D11" s="5" t="n">
         <v>254.189</v>
       </c>
+      <c r="E11" s="5" t="n">
+        <v>509.029</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1326,6 +1362,9 @@
       <c r="D12" s="5" t="n">
         <v>349.451</v>
       </c>
+      <c r="E12" s="5" t="n">
+        <v>626.2190000000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1339,6 +1378,9 @@
       <c r="D13" s="5" t="n">
         <v>-255.741</v>
       </c>
+      <c r="E13" s="5" t="n">
+        <v>-652.579</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1352,6 +1394,9 @@
       <c r="D14" s="11" t="n">
         <v>-0.4751183425356885</v>
       </c>
+      <c r="E14" s="11" t="n">
+        <v>-0.9204256153411087</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1365,6 +1410,9 @@
       <c r="D16" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1378,6 +1426,9 @@
       <c r="D17" s="5" t="n">
         <v>4.243</v>
       </c>
+      <c r="E17" s="5" t="n">
+        <v>11.335</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1391,6 +1442,9 @@
       <c r="D18" s="5" t="n">
         <v>-354.51</v>
       </c>
+      <c r="E18" s="5" t="n">
+        <v>-679.388</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1404,6 +1458,9 @@
       <c r="D19" s="11" t="n">
         <v>-0.6586124384135784</v>
       </c>
+      <c r="E19" s="11" t="n">
+        <v>-0.9582381871855593</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1417,6 +1474,9 @@
       <c r="D21" s="5" t="n">
         <v>-204.197</v>
       </c>
+      <c r="E21" s="5" t="n">
+        <v>-606.677</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1430,6 +1490,9 @@
       <c r="D22" s="11" t="n">
         <v>-0.3793593525901596</v>
       </c>
+      <c r="E22" s="11" t="n">
+        <v>-0.8556834514109368</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1441,7 +1504,10 @@
         <v>-1.051523</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>-1.88</v>
+        <v>-1.080973</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>-3.18</v>
       </c>
     </row>
     <row r="24">
@@ -1455,6 +1521,9 @@
       </c>
       <c r="D24" s="5" t="n">
         <v>51.544</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>45.902</v>
       </c>
     </row>
     <row r="27">
@@ -1466,6 +1535,7 @@
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="1" t="n"/>
       <c r="D27" s="1" t="n"/>
+      <c r="E27" s="1" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1479,6 +1549,9 @@
       <c r="D28" s="5" t="n">
         <v>166.012</v>
       </c>
+      <c r="E28" s="5" t="n">
+        <v>432.583</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1492,6 +1565,9 @@
       <c r="D29" s="5" t="n">
         <v>528.405</v>
       </c>
+      <c r="E29" s="5" t="n">
+        <v>1448.967</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1505,6 +1581,9 @@
       <c r="D30" s="5" t="n">
         <v>134.051</v>
       </c>
+      <c r="E30" s="5" t="n">
+        <v>125.972</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1518,6 +1597,9 @@
       <c r="D31" s="5" t="n">
         <v>61.083</v>
       </c>
+      <c r="E31" s="5" t="n">
+        <v>61.083</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1531,6 +1613,9 @@
       <c r="D32" s="5" t="n">
         <v>858.506</v>
       </c>
+      <c r="E32" s="5" t="n">
+        <v>1772.292</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1544,6 +1629,9 @@
       <c r="D34" s="5" t="n">
         <v>526.708</v>
       </c>
+      <c r="E34" s="5" t="n">
+        <v>681.532</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1557,6 +1645,9 @@
       <c r="D35" s="5" t="n">
         <v>662.697</v>
       </c>
+      <c r="E35" s="5" t="n">
+        <v>755.153</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1570,6 +1661,9 @@
       <c r="D36" s="5" t="n">
         <v>1344.095</v>
       </c>
+      <c r="E36" s="5" t="n">
+        <v>1577.761</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1582,6 +1676,9 @@
       </c>
       <c r="D38" s="5" t="n">
         <v>-485.589</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>194.531</v>
       </c>
     </row>
     <row r="41">
@@ -1593,6 +1690,7 @@
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="1" t="n"/>
       <c r="D41" s="1" t="n"/>
+      <c r="E41" s="1" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1606,6 +1704,9 @@
       <c r="D42" s="5" t="n">
         <v>-110.678</v>
       </c>
+      <c r="E42" s="5" t="n">
+        <v>38.073</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -1619,6 +1720,9 @@
       <c r="D43" s="5" t="n">
         <v>-40.422</v>
       </c>
+      <c r="E43" s="5" t="n">
+        <v>-25.7</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1632,6 +1736,9 @@
       <c r="D44" s="5" t="n">
         <v>-151.1</v>
       </c>
+      <c r="E44" s="5" t="n">
+        <v>12.373</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -1645,6 +1752,9 @@
       <c r="D46" s="5" t="n">
         <v>51.544</v>
       </c>
+      <c r="E46" s="5" t="n">
+        <v>45.902</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -1658,6 +1768,9 @@
       <c r="D47" s="5" t="n">
         <v>50.834</v>
       </c>
+      <c r="E47" s="5" t="n">
+        <v>516.191</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -1670,6 +1783,9 @@
       </c>
       <c r="D48" s="5" t="n">
         <v>-10.466</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>58.206</v>
       </c>
     </row>
   </sheetData>
@@ -1684,7 +1800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I206"/>
+  <dimension ref="A1:J206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1696,6 +1812,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1712,6 +1829,7 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1765,29 +1883,34 @@
           <t>FY2030</t>
         </is>
       </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>FY2031</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="E5" s="14" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Proj.</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Proj.</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>Proj.</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Proj.</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Proj.</t>
         </is>
@@ -1807,6 +1930,7 @@
       <c r="G7" s="1" t="n"/>
       <c r="H7" s="1" t="n"/>
       <c r="I7" s="1" t="n"/>
+      <c r="J7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1820,9 +1944,8 @@
       <c r="D8" s="5" t="n">
         <v>538.268</v>
       </c>
-      <c r="E8" s="8">
-        <f>Assumptions!E12</f>
-        <v/>
+      <c r="E8" s="5" t="n">
+        <v>708.997</v>
       </c>
       <c r="F8" s="8">
         <f>Assumptions!F12</f>
@@ -1840,6 +1963,10 @@
         <f>Assumptions!I12</f>
         <v/>
       </c>
+      <c r="J8" s="8">
+        <f>Assumptions!J12</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1871,6 +1998,10 @@
         <f>IFERROR(I8/H8-1,"-")</f>
         <v/>
       </c>
+      <c r="J9" s="7">
+        <f>IFERROR(J8/I8-1,"-")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1906,6 +2037,10 @@
         <f>I8</f>
         <v/>
       </c>
+      <c r="J11" s="8">
+        <f>J8</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1935,6 +2070,10 @@
       </c>
       <c r="I12" s="7">
         <f>IFERROR(I11/H11-1,"-")</f>
+        <v/>
+      </c>
+      <c r="J12" s="7">
+        <f>IFERROR(J11/I11-1,"-")</f>
         <v/>
       </c>
     </row>
@@ -1952,6 +2091,7 @@
       <c r="G14" s="1" t="n"/>
       <c r="H14" s="1" t="n"/>
       <c r="I14" s="1" t="n"/>
+      <c r="J14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1987,6 +2127,10 @@
         <f>I11</f>
         <v/>
       </c>
+      <c r="J15" s="8">
+        <f>J11</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2000,9 +2144,8 @@
       <c r="D16" s="5" t="n">
         <v>190.369</v>
       </c>
-      <c r="E16" s="8">
-        <f>-E15*(1-Assumptions!E18)</f>
-        <v/>
+      <c r="E16" s="5" t="n">
+        <v>226.328</v>
       </c>
       <c r="F16" s="8">
         <f>-F15*(1-Assumptions!F18)</f>
@@ -2020,6 +2163,10 @@
         <f>-I15*(1-Assumptions!I18)</f>
         <v/>
       </c>
+      <c r="J16" s="8">
+        <f>-J15*(1-Assumptions!J18)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2055,6 +2202,10 @@
         <f>I15+I16</f>
         <v/>
       </c>
+      <c r="J17" s="8">
+        <f>J15+J16</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2090,6 +2241,10 @@
         <f>IFERROR(I17/I15,"-")</f>
         <v/>
       </c>
+      <c r="J18" s="7">
+        <f>IFERROR(J17/J15,"-")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2103,9 +2258,8 @@
       <c r="D20" s="5" t="n">
         <v>349.451</v>
       </c>
-      <c r="E20" s="8">
-        <f>-E15*Assumptions!E24</f>
-        <v/>
+      <c r="E20" s="5" t="n">
+        <v>626.2190000000001</v>
       </c>
       <c r="F20" s="8">
         <f>-F15*Assumptions!F24</f>
@@ -2123,6 +2277,10 @@
         <f>-I15*Assumptions!I24</f>
         <v/>
       </c>
+      <c r="J20" s="8">
+        <f>-J15*Assumptions!J24</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2136,9 +2294,8 @@
       <c r="D21" s="5" t="n">
         <v>254.189</v>
       </c>
-      <c r="E21" s="8">
-        <f>-E15*Assumptions!E30</f>
-        <v/>
+      <c r="E21" s="5" t="n">
+        <v>509.029</v>
       </c>
       <c r="F21" s="8">
         <f>-F15*Assumptions!F30</f>
@@ -2156,6 +2313,10 @@
         <f>-I15*Assumptions!I30</f>
         <v/>
       </c>
+      <c r="J21" s="8">
+        <f>-J15*Assumptions!J30</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2169,9 +2330,8 @@
       <c r="D22" s="5" t="n">
         <v>51.544</v>
       </c>
-      <c r="E22" s="8">
-        <f>-E15*Assumptions!E32</f>
-        <v/>
+      <c r="E22" s="5" t="n">
+        <v>45.902</v>
       </c>
       <c r="F22" s="8">
         <f>-F15*Assumptions!F32</f>
@@ -2189,6 +2349,10 @@
         <f>-I15*Assumptions!I32</f>
         <v/>
       </c>
+      <c r="J22" s="8">
+        <f>-J15*Assumptions!J32</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2224,6 +2388,10 @@
         <f>I17+I20+I21</f>
         <v/>
       </c>
+      <c r="J24" s="8">
+        <f>J17+J20+J21</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2259,6 +2427,10 @@
         <f>IFERROR(I24/I15,"-")</f>
         <v/>
       </c>
+      <c r="J25" s="7">
+        <f>IFERROR(J24/J15,"-")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2294,6 +2466,10 @@
         <f>I24+I22</f>
         <v/>
       </c>
+      <c r="J26" s="8">
+        <f>J24+J22</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2329,6 +2505,10 @@
         <f>IFERROR(I26/I15,"-")</f>
         <v/>
       </c>
+      <c r="J27" s="7">
+        <f>IFERROR(J26/J15,"-")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2357,6 +2537,9 @@
       <c r="I29" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="J29" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2392,6 +2575,10 @@
         <f>I26+I29</f>
         <v/>
       </c>
+      <c r="J30" s="8">
+        <f>J26+J29</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2405,9 +2592,8 @@
       <c r="D31" s="5" t="n">
         <v>4.243</v>
       </c>
-      <c r="E31" s="8">
-        <f>-ABS(E30)*Assumptions!E34</f>
-        <v/>
+      <c r="E31" s="5" t="n">
+        <v>11.335</v>
       </c>
       <c r="F31" s="8">
         <f>-ABS(F30)*Assumptions!F34</f>
@@ -2425,6 +2611,10 @@
         <f>-ABS(I30)*Assumptions!I34</f>
         <v/>
       </c>
+      <c r="J31" s="8">
+        <f>-ABS(J30)*Assumptions!J34</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2460,6 +2650,10 @@
         <f>I30+I31</f>
         <v/>
       </c>
+      <c r="J32" s="8">
+        <f>J30+J31</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2493,6 +2687,10 @@
       </c>
       <c r="I33" s="7">
         <f>IFERROR(I32/I15,"-")</f>
+        <v/>
+      </c>
+      <c r="J33" s="7">
+        <f>IFERROR(J32/J15,"-")</f>
         <v/>
       </c>
     </row>
@@ -2510,6 +2708,7 @@
       <c r="G36" s="1" t="n"/>
       <c r="H36" s="1" t="n"/>
       <c r="I36" s="1" t="n"/>
+      <c r="J36" s="1" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2545,6 +2744,10 @@
         <f>I24</f>
         <v/>
       </c>
+      <c r="J37" s="8">
+        <f>J24</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -2580,6 +2783,10 @@
         <f>I31</f>
         <v/>
       </c>
+      <c r="J38" s="8">
+        <f>J31</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2594,7 +2801,7 @@
         <v>-10.466</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>58.206</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>0</v>
@@ -2608,6 +2815,9 @@
       <c r="I39" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="J39" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2643,6 +2853,10 @@
         <f>I37+I38+I39</f>
         <v/>
       </c>
+      <c r="J40" s="8">
+        <f>J37+J38+J39</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -2656,9 +2870,8 @@
       <c r="D42" s="5" t="n">
         <v>-40.422</v>
       </c>
-      <c r="E42" s="8">
-        <f>-ABS(E15)*Assumptions!E33</f>
-        <v/>
+      <c r="E42" s="5" t="n">
+        <v>-25.7</v>
       </c>
       <c r="F42" s="8">
         <f>-ABS(F15)*Assumptions!F33</f>
@@ -2676,6 +2889,10 @@
         <f>-ABS(I15)*Assumptions!I33</f>
         <v/>
       </c>
+      <c r="J42" s="8">
+        <f>-ABS(J15)*Assumptions!J33</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2709,6 +2926,10 @@
       </c>
       <c r="I43" s="8">
         <f>I40+I42</f>
+        <v/>
+      </c>
+      <c r="J43" s="8">
+        <f>J40+J42</f>
         <v/>
       </c>
     </row>
@@ -2806,6 +3027,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2822,6 +3044,7 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2839,7 +3062,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>7.73</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="4">
@@ -2848,9 +3071,6 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>2026</v>
-      </c>
       <c r="F4" s="1" t="n">
         <v>2027</v>
       </c>
@@ -2863,6 +3083,9 @@
       <c r="I4" s="1" t="n">
         <v>2030</v>
       </c>
+      <c r="J4" s="1" t="n">
+        <v>2031</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2870,19 +3093,19 @@
           <t>Year #</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2900,6 +3123,7 @@
       <c r="G7" s="1" t="n"/>
       <c r="H7" s="1" t="n"/>
       <c r="I7" s="1" t="n"/>
+      <c r="J7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2907,10 +3131,6 @@
           <t>EBITDA ($M)</t>
         </is>
       </c>
-      <c r="E8" s="8">
-        <f>INDIRECT("Model!"&amp;"E"&amp;Model!B200)</f>
-        <v/>
-      </c>
       <c r="F8" s="8">
         <f>INDIRECT("Model!"&amp;"F"&amp;Model!B200)</f>
         <v/>
@@ -2927,6 +3147,10 @@
         <f>INDIRECT("Model!"&amp;"I"&amp;Model!B200)</f>
         <v/>
       </c>
+      <c r="J8" s="8">
+        <f>INDIRECT("Model!"&amp;"J"&amp;Model!B200)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2934,10 +3158,6 @@
           <t>(-) Taxes ($M)</t>
         </is>
       </c>
-      <c r="E9" s="8">
-        <f>INDIRECT("Model!"&amp;"E"&amp;Model!B201)</f>
-        <v/>
-      </c>
       <c r="F9" s="8">
         <f>INDIRECT("Model!"&amp;"F"&amp;Model!B201)</f>
         <v/>
@@ -2954,6 +3174,10 @@
         <f>INDIRECT("Model!"&amp;"I"&amp;Model!B201)</f>
         <v/>
       </c>
+      <c r="J9" s="8">
+        <f>INDIRECT("Model!"&amp;"J"&amp;Model!B201)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2961,10 +3185,6 @@
           <t>(+/-) Change in WC ($M)</t>
         </is>
       </c>
-      <c r="E10" s="8">
-        <f>INDIRECT("Model!"&amp;"E"&amp;Model!B204)</f>
-        <v/>
-      </c>
       <c r="F10" s="8">
         <f>INDIRECT("Model!"&amp;"F"&amp;Model!B204)</f>
         <v/>
@@ -2981,6 +3201,10 @@
         <f>INDIRECT("Model!"&amp;"I"&amp;Model!B204)</f>
         <v/>
       </c>
+      <c r="J10" s="8">
+        <f>INDIRECT("Model!"&amp;"J"&amp;Model!B204)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2988,10 +3212,6 @@
           <t>(-) CapEx ($M)</t>
         </is>
       </c>
-      <c r="E11" s="8">
-        <f>INDIRECT("Model!"&amp;"E"&amp;Model!B202)</f>
-        <v/>
-      </c>
       <c r="F11" s="8">
         <f>INDIRECT("Model!"&amp;"F"&amp;Model!B202)</f>
         <v/>
@@ -3008,6 +3228,10 @@
         <f>INDIRECT("Model!"&amp;"I"&amp;Model!B202)</f>
         <v/>
       </c>
+      <c r="J11" s="8">
+        <f>INDIRECT("Model!"&amp;"J"&amp;Model!B202)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3015,10 +3239,6 @@
           <t>Unlevered Free Cash Flow ($M)</t>
         </is>
       </c>
-      <c r="E12" s="8">
-        <f>E8+E9+E10+E11</f>
-        <v/>
-      </c>
       <c r="F12" s="8">
         <f>F8+F9+F10+F11</f>
         <v/>
@@ -3033,6 +3253,10 @@
       </c>
       <c r="I12" s="8">
         <f>I8+I9+I10+I11</f>
+        <v/>
+      </c>
+      <c r="J12" s="8">
+        <f>J8+J9+J10+J11</f>
         <v/>
       </c>
     </row>
@@ -3050,6 +3274,7 @@
       <c r="G14" s="1" t="n"/>
       <c r="H14" s="1" t="n"/>
       <c r="I14" s="1" t="n"/>
+      <c r="J14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3079,23 +3304,23 @@
           <t>Discount Factor</t>
         </is>
       </c>
-      <c r="E18" s="17">
+      <c r="F18" s="17">
         <f>1/(1+$C$15)^1</f>
         <v/>
       </c>
-      <c r="F18" s="17">
+      <c r="G18" s="17">
         <f>1/(1+$C$15)^2</f>
         <v/>
       </c>
-      <c r="G18" s="17">
+      <c r="H18" s="17">
         <f>1/(1+$C$15)^3</f>
         <v/>
       </c>
-      <c r="H18" s="17">
+      <c r="I18" s="17">
         <f>1/(1+$C$15)^4</f>
         <v/>
       </c>
-      <c r="I18" s="17">
+      <c r="J18" s="17">
         <f>1/(1+$C$15)^5</f>
         <v/>
       </c>
@@ -3106,10 +3331,6 @@
           <t>PV of UFCF ($M)</t>
         </is>
       </c>
-      <c r="E19" s="8">
-        <f>E12*E18</f>
-        <v/>
-      </c>
       <c r="F19" s="8">
         <f>F12*F18</f>
         <v/>
@@ -3126,6 +3347,10 @@
         <f>I12*I18</f>
         <v/>
       </c>
+      <c r="J19" s="8">
+        <f>J12*J18</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3133,8 +3358,8 @@
           <t>Terminal Value ($M)</t>
         </is>
       </c>
-      <c r="I21" s="8">
-        <f>I8*$C$16</f>
+      <c r="J21" s="8">
+        <f>J8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3144,8 +3369,8 @@
           <t>PV of Terminal Value ($M)</t>
         </is>
       </c>
-      <c r="I22" s="8">
-        <f>I21*I18</f>
+      <c r="J22" s="8">
+        <f>J21*J18</f>
         <v/>
       </c>
     </row>
@@ -3163,6 +3388,7 @@
       <c r="G24" s="1" t="n"/>
       <c r="H24" s="1" t="n"/>
       <c r="I24" s="1" t="n"/>
+      <c r="J24" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3171,7 +3397,7 @@
         </is>
       </c>
       <c r="C25" s="8">
-        <f>SUM(E19:I19)</f>
+        <f>SUM(F19:J19)</f>
         <v/>
       </c>
     </row>
@@ -3182,7 +3408,7 @@
         </is>
       </c>
       <c r="C26" s="8">
-        <f>I22</f>
+        <f>J22</f>
         <v/>
       </c>
     </row>
@@ -3204,7 +3430,7 @@
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>-496.685</v>
+        <v>-322.57</v>
       </c>
     </row>
     <row r="30">
@@ -3246,7 +3472,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/7.73-1</f>
+        <f>C33/9.07-1</f>
         <v/>
       </c>
     </row>
@@ -3275,202 +3501,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>21x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>23x</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>6x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>27x</t>
+          <t>8x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>29x</t>
+          <t>10x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0605</v>
+        <v>0.08</v>
       </c>
       <c r="C39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*21/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*2/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*23/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*4/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*25/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*6/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*27/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*8/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*29/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*10/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="C40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*21/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*2/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*23/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*4/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*25/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*6/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*27/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*8/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*29/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*10/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0805</v>
+        <v>0.1</v>
       </c>
       <c r="C41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*21/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*2/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*23/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*4/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*25/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*6/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*27/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*8/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*29/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*10/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.0905</v>
+        <v>0.11</v>
       </c>
       <c r="C42" s="22">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*21/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*2/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*23/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*4/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*25/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*6/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*27/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*8/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*29/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*10/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.1005</v>
+        <v>0.12</v>
       </c>
       <c r="C43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*21/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*2/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*23/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*4/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*25/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*6/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*27/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*8/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*29/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*10/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1105</v>
+        <v>0.13</v>
       </c>
       <c r="C44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*21/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*2/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*23/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*4/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*25/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*6/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*27/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*8/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*29/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*10/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1205</v>
+        <v>0.14</v>
       </c>
       <c r="C45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*21/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*2/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*23/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*4/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*25/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*6/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*27/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*8/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*29/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*10/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
